--- a/results/Int Task Remove ACC -0.5/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC -0.5/Rando_6_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6509306052015285</v>
+        <v>0.6797629319199638</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6321079337688484</v>
+        <v>0.6898753030116275</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6268848350384157</v>
+        <v>0.6919758412424504</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6279530794198611</v>
+        <v>0.6952370680800362</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6302744566333868</v>
+        <v>0.6973581494720408</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6258525411890381</v>
+        <v>0.6912671021816837</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6258525411890381</v>
+        <v>0.686105632934796</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6218414889683225</v>
+        <v>0.698462344385554</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6163051070298697</v>
+        <v>0.6805795225769341</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6081854225728255</v>
+        <v>0.6797013024364189</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6084576194584823</v>
+        <v>0.6801892025144829</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.604302765109495</v>
+        <v>0.6831063314022763</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6136653108180288</v>
+        <v>0.6873279510251037</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6302179629401372</v>
+        <v>0.6873279510251037</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6302795924236821</v>
+        <v>0.6795318213566703</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6310961830806524</v>
+        <v>0.6789257981018119</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6194328033197749</v>
+        <v>0.6740622046920579</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6153960721475821</v>
+        <v>0.6721157401700973</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.603065039648301</v>
+        <v>0.6692191544434858</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6027825711820535</v>
+        <v>0.676825259870989</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6111744525247546</v>
+        <v>0.6698251776983442</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6319230453182136</v>
+        <v>0.6649204979662271</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6149646657627676</v>
+        <v>0.6667180245696207</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6102551460618759</v>
+        <v>0.678489255926702</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6109227988002794</v>
+        <v>0.67915177287481</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6109227988002794</v>
+        <v>0.6778575537203665</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6064957475656354</v>
+        <v>0.6718178643329635</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6104657134639879</v>
+        <v>0.6651772874809976</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5974156703233493</v>
+        <v>0.6570113809112946</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6078926825259872</v>
+        <v>0.6534676856074613</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6086014215867538</v>
+        <v>0.656564567155594</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6085757426352767</v>
+        <v>0.6553114343235137</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6066960433871564</v>
+        <v>0.6562923702699371</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.59648609227988</v>
+        <v>0.6594508813016147</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.59648609227988</v>
+        <v>0.6672624183409342</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6172809071859977</v>
+        <v>0.6559174575783722</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6295554459920292</v>
+        <v>0.6422100332799211</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6398218907925551</v>
+        <v>0.6477875015407371</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6396164591807387</v>
+        <v>0.6392415464891738</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.640556308804799</v>
+        <v>0.6490765849048852</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6403868277250503</v>
+        <v>0.6557787912403961</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6387844611528822</v>
+        <v>0.6518550474547024</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6374183409343029</v>
+        <v>0.6105787008504868</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6363963186655162</v>
+        <v>0.5995675664571264</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6489841406795678</v>
+        <v>0.6274035498582522</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6508022104441431</v>
+        <v>0.6304952956160894</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6550238300669707</v>
+        <v>0.6346193352233042</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.675849459714861</v>
+        <v>0.6349120752701426</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6714686305928756</v>
+        <v>0.6349120752701426</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6714686305928756</v>
+        <v>0.6153498500349234</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6714686305928756</v>
+        <v>0.6116212662804552</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6405152224824355</v>
+        <v>0.5843861703438925</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6167005628826163</v>
+        <v>0.569898105920539</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5753677225851515</v>
+        <v>0.5790603558075517</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5627131352972595</v>
+        <v>0.5704373639015572</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5466072969308517</v>
+        <v>0.5711615103332101</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.54658675376967</v>
+        <v>0.574011873947163</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5444194502650067</v>
+        <v>0.561531903529315</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5429557500308148</v>
+        <v>0.515058137146144</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5027887341304079</v>
+        <v>0.5162907268170426</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4976324006738156</v>
+        <v>0.5218938740293356</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4870732158264514</v>
+        <v>0.5248726324006738</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4845977649040635</v>
+        <v>0.5216781708369284</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4845977649040635</v>
+        <v>0.5395096347425942</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4935751263404413</v>
+        <v>0.5406600517687662</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4939757179834833</v>
+        <v>0.5450562882616377</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5035128805620609</v>
+        <v>0.5143750770368545</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5041651259295781</v>
+        <v>0.514082336990016</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5058804798882452</v>
+        <v>0.5180574386786638</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5046324828464605</v>
+        <v>0.5136612021857924</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4886858539792103</v>
+        <v>0.5151916676938247</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4961738362299191</v>
+        <v>0.5161520604790666</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4866264020707507</v>
+        <v>0.5130346357697523</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4797393072846049</v>
+        <v>0.5130346357697523</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4733503841571141</v>
+        <v>0.513620115863429</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4702072804963228</v>
+        <v>0.5125107851596203</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4670128189325773</v>
+        <v>0.5104975553638194</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4644295164139858</v>
+        <v>0.5101637289946177</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4750092444225317</v>
+        <v>0.5090954846131722</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4829080898968733</v>
+        <v>0.5205072106495747</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4949258391881343</v>
+        <v>0.5219760466740622</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4914386375775504</v>
+        <v>0.5101842721557993</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4946741854636592</v>
+        <v>0.5045913965240971</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4993734335839599</v>
+        <v>0.4998561978717285</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.49968671679198</v>
+        <v>0.4955421340235835</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5002927400468384</v>
+        <v>0.4934570031636468</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5002927400468384</v>
+        <v>0.4946639138830684</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.4917981428982292</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.4907042195653067</v>
       </c>
     </row>
   </sheetData>
